--- a/data/trans_dic/P16A13-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,34</t>
+          <t>1,68; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,2</t>
+          <t>2,49; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,94</t>
+          <t>2,59; 6,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,43</t>
+          <t>5,53; 9,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,93</t>
+          <t>0,64; 3,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,38</t>
+          <t>3,55; 9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,94</t>
+          <t>1,48; 5,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,95</t>
+          <t>3,12; 6,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,13</t>
+          <t>1,75; 4,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,26</t>
+          <t>3,5; 7,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,62</t>
+          <t>2,49; 5,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,2</t>
+          <t>4,72; 7,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,56</t>
+          <t>0,99; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,98</t>
+          <t>1,7; 5,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,71</t>
+          <t>1,72; 5,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,17</t>
+          <t>4,05; 8,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,31</t>
+          <t>1,6; 5,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,74</t>
+          <t>2,55; 7,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,59</t>
+          <t>2,42; 7,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,15</t>
+          <t>3,45; 6,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,25</t>
+          <t>1,66; 3,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,94</t>
+          <t>2,56; 5,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,56</t>
+          <t>2,45; 5,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,8</t>
+          <t>3,99; 6,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,81</t>
+          <t>1,21; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,28</t>
+          <t>2,08; 5,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,77</t>
+          <t>1,66; 4,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,99</t>
+          <t>1,95; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,58</t>
+          <t>2,83; 9,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,96</t>
+          <t>2,35; 8,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,54</t>
+          <t>2,67; 11,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,28</t>
+          <t>8,33; 15,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,38</t>
+          <t>1,84; 4,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,29</t>
+          <t>2,52; 5,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,61</t>
+          <t>2,43; 5,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,59</t>
+          <t>2,84; 9,63</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,2</t>
+          <t>2,08; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,81</t>
+          <t>4,05; 6,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,06</t>
+          <t>1,37; 3,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,79</t>
+          <t>5,16; 7,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,35</t>
+          <t>1,91; 4,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,24</t>
+          <t>2,97; 6,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,23</t>
+          <t>2,52; 5,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,75</t>
+          <t>2,67; 7,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,83</t>
+          <t>2,32; 3,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,07</t>
+          <t>4,0; 6,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,52</t>
+          <t>2,04; 3,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,24</t>
+          <t>4,16; 7,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,55</t>
+          <t>1,76; 5,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,06</t>
+          <t>2,42; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,29</t>
+          <t>2,77; 6,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,79</t>
+          <t>5,14; 11,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,74</t>
+          <t>1,83; 4,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,14</t>
+          <t>5,15; 9,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,42</t>
+          <t>2,29; 5,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,1</t>
+          <t>8,07; 13,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,47</t>
+          <t>2,1; 4,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,11</t>
+          <t>4,39; 7,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,08</t>
+          <t>2,96; 5,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,46</t>
+          <t>7,75; 11,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,16</t>
+          <t>0,5; 4,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,6</t>
+          <t>0,51; 3,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,95</t>
+          <t>3,46; 5,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,55</t>
+          <t>3,96; 6,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,09</t>
+          <t>3,37; 6,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,67</t>
+          <t>8,56; 11,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,89</t>
+          <t>2,95; 4,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,83</t>
+          <t>3,47; 5,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,99</t>
+          <t>2,67; 4,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,32</t>
+          <t>6,75; 9,43</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,26</t>
+          <t>2,1; 3,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,95</t>
+          <t>3,42; 4,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,58</t>
+          <t>2,32; 3,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,93</t>
+          <t>4,73; 6,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,31</t>
+          <t>2,95; 4,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,24</t>
+          <t>4,64; 6,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,86</t>
+          <t>3,44; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,85</t>
+          <t>6,32; 8,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,61</t>
+          <t>2,71; 3,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 5,32</t>
+          <t>4,22; 5,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,98</t>
+          <t>3,08; 4,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,69</t>
+          <t>6,03; 7,66</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8666; 25295</t>
+          <t>7954; 24371</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10096; 31459</t>
+          <t>10872; 33174</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11043; 29774</t>
+          <t>11096; 29159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27480; 47639</t>
+          <t>27951; 48348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2682; 12048</t>
+          <t>1963; 11829</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11263; 29502</t>
+          <t>11171; 28979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5113; 20603</t>
+          <t>5134; 20794</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14024; 26637</t>
+          <t>13970; 26946</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13325; 32229</t>
+          <t>13676; 34021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25239; 54546</t>
+          <t>26274; 53997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19418; 43633</t>
+          <t>19363; 43425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44906; 68596</t>
+          <t>44935; 68404</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3889; 16747</t>
+          <t>3639; 17026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6930; 24940</t>
+          <t>7096; 23639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6868; 21543</t>
+          <t>6494; 21565</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18121; 36933</t>
+          <t>18329; 36883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6145; 19751</t>
+          <t>5944; 19700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8505; 25943</t>
+          <t>8546; 26088</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8792; 28244</t>
+          <t>8997; 26868</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12660; 27338</t>
+          <t>13184; 26718</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12700; 31371</t>
+          <t>12254; 29246</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18909; 44713</t>
+          <t>19272; 43225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18406; 41672</t>
+          <t>18380; 42709</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34670; 56744</t>
+          <t>33312; 56072</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6408; 20691</t>
+          <t>6571; 20168</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13178; 33032</t>
+          <t>12986; 32496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8299; 24904</t>
+          <t>8650; 25478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12301; 60045</t>
+          <t>13011; 60909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3887; 16079</t>
+          <t>4748; 16212</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5833; 20539</t>
+          <t>6064; 20974</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4279; 19171</t>
+          <t>4440; 19486</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14061; 25504</t>
+          <t>13908; 25495</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13523; 31072</t>
+          <t>13094; 30403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23989; 46713</t>
+          <t>22243; 46872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16555; 38632</t>
+          <t>16711; 38877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23808; 80114</t>
+          <t>23751; 80450</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28135; 52019</t>
+          <t>25755; 51437</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46303; 78633</t>
+          <t>46779; 78431</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15914; 35150</t>
+          <t>15780; 35553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53633; 80644</t>
+          <t>53381; 81666</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13723; 31107</t>
+          <t>13672; 31624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23907; 47836</t>
+          <t>22763; 47094</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20629; 43187</t>
+          <t>20849; 45381</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30623; 75798</t>
+          <t>26109; 76642</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44795; 74717</t>
+          <t>45268; 75652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77510; 116625</t>
+          <t>76774; 115730</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41699; 69449</t>
+          <t>40314; 70302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80319; 145734</t>
+          <t>83707; 145208</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5817; 19406</t>
+          <t>6151; 19265</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11603; 30959</t>
+          <t>12342; 31103</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17986; 39071</t>
+          <t>17212; 37819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25127; 55901</t>
+          <t>24361; 54376</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10060; 26974</t>
+          <t>10388; 26324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39719; 69364</t>
+          <t>39129; 69720</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17552; 39993</t>
+          <t>16902; 39654</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67435; 109886</t>
+          <t>67696; 109660</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19933; 41024</t>
+          <t>19290; 40028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55597; 90262</t>
+          <t>55715; 91444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39522; 68973</t>
+          <t>40250; 69233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>103911; 150463</t>
+          <t>101696; 150600</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6740</t>
+          <t>0; 6438</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1867; 13713</t>
+          <t>1337; 12783</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4867</t>
+          <t>0; 5950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1172; 8666</t>
+          <t>1215; 8940</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43526; 74266</t>
+          <t>43211; 72317</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43525; 72388</t>
+          <t>43822; 73198</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36150; 65921</t>
+          <t>36448; 66754</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64642; 88683</t>
+          <t>65039; 89369</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44773; 75638</t>
+          <t>45661; 76218</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48163; 79896</t>
+          <t>47515; 81176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37082; 68261</t>
+          <t>36500; 67508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68252; 93263</t>
+          <t>67558; 94384</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>69958; 106641</t>
+          <t>68687; 105792</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>119301; 169002</t>
+          <t>116721; 166001</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79710; 121298</t>
+          <t>78676; 118530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>158425; 233822</t>
+          <t>159567; 235617</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>101175; 145504</t>
+          <t>99801; 142997</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161993; 220762</t>
+          <t>164149; 215562</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>120198; 171532</t>
+          <t>121427; 171555</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>234246; 316297</t>
+          <t>226022; 314157</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>181637; 240278</t>
+          <t>179873; 236167</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>295244; 369490</t>
+          <t>293285; 367589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>211402; 275323</t>
+          <t>213182; 276902</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>425624; 534506</t>
+          <t>418661; 532388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A13-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,14</t>
+          <t>1,85; 5,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,59</t>
+          <t>2,54; 7,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,8</t>
+          <t>2,5; 6,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,57</t>
+          <t>4,98; 8,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,86</t>
+          <t>0,67; 4,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,22</t>
+          <t>3,59; 9,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,99</t>
+          <t>1,4; 5,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,02</t>
+          <t>3,25; 6,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,36</t>
+          <t>1,66; 4,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,18</t>
+          <t>3,44; 7,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,6</t>
+          <t>2,53; 5,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,18</t>
+          <t>4,6; 6,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,64</t>
+          <t>1,03; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,67</t>
+          <t>1,52; 5,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,72</t>
+          <t>1,61; 5,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,16</t>
+          <t>3,95; 7,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,3</t>
+          <t>1,63; 5,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,78</t>
+          <t>2,55; 8,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,22</t>
+          <t>2,24; 7,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,98</t>
+          <t>3,33; 6,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,96</t>
+          <t>1,54; 3,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,75</t>
+          <t>2,54; 5,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,7</t>
+          <t>2,49; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,72</t>
+          <t>4,03; 6,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,72</t>
+          <t>1,23; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,2</t>
+          <t>2,14; 5,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,88</t>
+          <t>1,66; 4,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,11</t>
+          <t>5,76; 10,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,66</t>
+          <t>2,33; 9,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,13</t>
+          <t>2,32; 7,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,73</t>
+          <t>2,74; 11,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 15,27</t>
+          <t>8,4; 15,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,28</t>
+          <t>1,87; 4,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,31</t>
+          <t>2,65; 5,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,65</t>
+          <t>2,45; 5,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,63</t>
+          <t>7,1; 11,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,15</t>
+          <t>2,2; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,79</t>
+          <t>4,1; 6,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,89</t>
+          <t>5,46; 8,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,43</t>
+          <t>1,97; 4,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,14</t>
+          <t>2,95; 6,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,49</t>
+          <t>2,56; 5,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,84</t>
+          <t>5,86; 8,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,87</t>
+          <t>2,24; 3,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,02</t>
+          <t>4,03; 6,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,56</t>
+          <t>2,05; 3,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,22</t>
+          <t>5,9; 7,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,51</t>
+          <t>1,76; 5,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,09</t>
+          <t>2,41; 6,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,09</t>
+          <t>2,9; 6,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,47</t>
+          <t>4,51; 8,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,63</t>
+          <t>2,0; 5,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,18</t>
+          <t>5,21; 8,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,37</t>
+          <t>2,41; 5,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,07</t>
+          <t>10,54; 13,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,36</t>
+          <t>2,12; 4,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,2</t>
+          <t>4,48; 7,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,09</t>
+          <t>2,81; 5,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,47</t>
+          <t>8,63; 11,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,81</t>
+          <t>0,39; 4,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,72</t>
+          <t>0,57; 3,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,79</t>
+          <t>3,45; 5,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,62</t>
+          <t>3,99; 6,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,17</t>
+          <t>3,49; 6,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 11,76</t>
+          <t>8,34; 11,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,93</t>
+          <t>2,97; 4,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,92</t>
+          <t>3,46; 5,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,93</t>
+          <t>2,73; 4,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,43</t>
+          <t>6,88; 9,39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,24</t>
+          <t>2,15; 3,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,87</t>
+          <t>3,35; 4,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,5</t>
+          <t>2,31; 3,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 6,98</t>
+          <t>5,53; 7,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,23</t>
+          <t>3,0; 4,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,09</t>
+          <t>4,52; 6,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,86</t>
+          <t>3,37; 4,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,79</t>
+          <t>7,81; 9,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,55</t>
+          <t>2,72; 3,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,29</t>
+          <t>4,25; 5,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,0</t>
+          <t>3,05; 3,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,66</t>
+          <t>6,87; 7,93</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36548</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56162</t>
+          <t>59687</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7954; 24371</t>
+          <t>8752; 24422</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10872; 33174</t>
+          <t>11108; 30817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11096; 29159</t>
+          <t>10716; 28723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27951; 48348</t>
+          <t>27413; 47951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1963; 11829</t>
+          <t>2051; 12439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11171; 28979</t>
+          <t>11299; 28529</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5134; 20794</t>
+          <t>4843; 20129</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13970; 26946</t>
+          <t>15858; 30093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13676; 34021</t>
+          <t>12925; 31344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26274; 53997</t>
+          <t>25843; 53843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19363; 43425</t>
+          <t>19628; 43335</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44935; 68404</t>
+          <t>47837; 71953</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>46948</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3639; 17026</t>
+          <t>3795; 15831</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7096; 23639</t>
+          <t>6322; 23590</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6494; 21565</t>
+          <t>6081; 20827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18329; 36883</t>
+          <t>19096; 38086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5944; 19700</t>
+          <t>6071; 18917</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8546; 26088</t>
+          <t>8542; 26809</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8997; 26868</t>
+          <t>8348; 26264</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13184; 26718</t>
+          <t>14082; 27619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12254; 29246</t>
+          <t>11387; 29476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19272; 43225</t>
+          <t>19084; 43005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18380; 42709</t>
+          <t>18639; 41597</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33312; 56072</t>
+          <t>36551; 59375</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>58027</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6571; 20168</t>
+          <t>6653; 20689</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12986; 32496</t>
+          <t>13358; 32122</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8650; 25478</t>
+          <t>8684; 25061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13011; 60909</t>
+          <t>27177; 48195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4748; 16212</t>
+          <t>3907; 16238</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6064; 20974</t>
+          <t>5972; 20373</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4440; 19486</t>
+          <t>4559; 19518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13908; 25495</t>
+          <t>15741; 28618</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13094; 30403</t>
+          <t>13266; 30721</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22243; 46872</t>
+          <t>23443; 46919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16711; 38877</t>
+          <t>16830; 38529</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23751; 80450</t>
+          <t>46806; 72630</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66710</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>122845</t>
+          <t>135504</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25755; 51437</t>
+          <t>27295; 51099</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46779; 78431</t>
+          <t>47363; 78254</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15780; 35553</t>
+          <t>15757; 35539</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53381; 81666</t>
+          <t>61795; 91212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13672; 31624</t>
+          <t>14100; 31063</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22763; 47094</t>
+          <t>22639; 48359</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20849; 45381</t>
+          <t>21161; 43988</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26109; 76642</t>
+          <t>50395; 74080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45268; 75652</t>
+          <t>43714; 74080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76774; 115730</t>
+          <t>77513; 117317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40314; 70302</t>
+          <t>40507; 70871</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83707; 145208</t>
+          <t>117516; 155283</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92396</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>127444</t>
+          <t>136221</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6151; 19265</t>
+          <t>6137; 19720</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12342; 31103</t>
+          <t>12293; 31260</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17212; 37819</t>
+          <t>18019; 37747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24361; 54376</t>
+          <t>25573; 47618</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10388; 26324</t>
+          <t>11400; 29678</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39129; 69720</t>
+          <t>39577; 67655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16902; 39654</t>
+          <t>17768; 39252</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67696; 109660</t>
+          <t>87465; 115463</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19290; 40028</t>
+          <t>19511; 41651</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55715; 91444</t>
+          <t>56889; 91092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40250; 69233</t>
+          <t>38240; 67891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>101696; 150600</t>
+          <t>120525; 155852</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>83344</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>86871</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6438</t>
+          <t>0; 7163</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1337; 12783</t>
+          <t>1023; 11721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 5474</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1215; 8940</t>
+          <t>1362; 8686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43211; 72317</t>
+          <t>43072; 73076</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43822; 73198</t>
+          <t>44058; 73021</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36448; 66754</t>
+          <t>37772; 68176</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>65039; 89369</t>
+          <t>70298; 98960</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>45661; 76218</t>
+          <t>45882; 75912</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47515; 81176</t>
+          <t>47466; 78360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36500; 67508</t>
+          <t>37434; 66505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67558; 94384</t>
+          <t>74272; 101474</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>202748</t>
+          <t>214733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>282707</t>
+          <t>308523</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>485455</t>
+          <t>523257</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>68687; 105792</t>
+          <t>70269; 108235</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116721; 166001</t>
+          <t>114404; 167069</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78676; 118530</t>
+          <t>78173; 118542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159567; 235617</t>
+          <t>190348; 241997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>99801; 142997</t>
+          <t>101258; 144108</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>164149; 215562</t>
+          <t>160010; 219109</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>121427; 171555</t>
+          <t>119127; 169373</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>226022; 314157</t>
+          <t>283811; 336202</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179873; 236167</t>
+          <t>180819; 236869</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293285; 367589</t>
+          <t>295467; 367454</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>213182; 276902</t>
+          <t>211136; 275676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>418661; 532388</t>
+          <t>485893; 560702</t>
         </is>
       </c>
     </row>
